--- a/Courses/Term 3/QAM-III/701 - DATA Price - Std and Deluxe bags.xlsx
+++ b/Courses/Term 3/QAM-III/701 - DATA Price - Std and Deluxe bags.xlsx
@@ -1,20 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suranjandas/Desktop/SIRMAUR. IIM .. Nov 14 2025/T1 - Non Linear Programming/SOLN.. for SD/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MBA\Courses\Term 3\QAM-III\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B7C48EC-DCEF-5E45-AF14-D07313307ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2222836-CB4A-410D-A25B-937342AF901C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1760" yWindow="1320" windowWidth="27640" windowHeight="16760" xr2:uid="{B2BED8D6-8C7E-0E42-9D17-93C443EBC8CA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{B2BED8D6-8C7E-0E42-9D17-93C443EBC8CA}"/>
   </bookViews>
   <sheets>
     <sheet name="Case 2" sheetId="2" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">'Case 2'!$C$18</definedName>
+    <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs1" localSheetId="0" hidden="1">'Case 2'!$D$17</definedName>
+    <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">'Case 2'!$G$18</definedName>
+    <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
+    <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_rhs1" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
+    <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t xml:space="preserve">Standard </t>
   </si>
@@ -68,6 +100,24 @@
   </si>
   <si>
     <t>B) What is the nature of the overall profit function of the business? What is the optimal solution and profit?</t>
+  </si>
+  <si>
+    <t>PRICE</t>
+  </si>
+  <si>
+    <t>REVENUE</t>
+  </si>
+  <si>
+    <t>COST</t>
+  </si>
+  <si>
+    <t>PROFIT</t>
+  </si>
+  <si>
+    <t>STANDARD</t>
+  </si>
+  <si>
+    <t>DELUXE</t>
   </si>
 </sst>
 </file>
@@ -123,9 +173,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -163,7 +213,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -269,7 +319,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -411,7 +461,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -419,15 +469,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44599672-B1FA-F740-90FA-32922E72A720}">
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -435,7 +485,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -446,7 +496,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -457,17 +507,91 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
     </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17">
+        <v>109.99999999999999</v>
+      </c>
+      <c r="D17">
+        <f>2250-15*C17</f>
+        <v>600.00000000000023</v>
+      </c>
+      <c r="E17">
+        <f>C17*D17</f>
+        <v>66000.000000000015</v>
+      </c>
+      <c r="F17">
+        <f>70*D17</f>
+        <v>42000.000000000015</v>
+      </c>
+      <c r="G17">
+        <f>E17-F17</f>
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18">
+        <v>225</v>
+      </c>
+      <c r="D18">
+        <f>1500-5*C18</f>
+        <v>375</v>
+      </c>
+      <c r="E18">
+        <f>C18*D18</f>
+        <v>84375</v>
+      </c>
+      <c r="F18">
+        <f>150*D18</f>
+        <v>56250</v>
+      </c>
+      <c r="G18">
+        <f>E18-F18</f>
+        <v>28125</v>
+      </c>
+    </row>
   </sheetData>
+  <scenarios current="0" show="0">
+    <scenario name="Max Profit of Standard Bags" locked="1" count="5" user="rohit ghosh" comment="Created by rohit ghosh on 05/01/2026">
+      <inputCells r="C17" val="1000"/>
+      <inputCells r="D17" val="2250"/>
+      <inputCells r="E17" val="0"/>
+      <inputCells r="F17" val="157500"/>
+      <inputCells r="G17" val="-157500"/>
+    </scenario>
+  </scenarios>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>